--- a/logs/activity_log.xlsx
+++ b/logs/activity_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +462,40 @@
         </is>
       </c>
       <c r="C3" t="inlineStr">
+        <is>
+          <t>Added new employee record</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2024-12-13 23:16:44</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>20241213-008</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Employee record saved successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2024-12-13 23:16:45</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20241213-008</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>Added new employee record</t>
         </is>

--- a/logs/activity_log.xlsx
+++ b/logs/activity_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,6 +501,244 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2024-12-13 23:22:30</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20241213-009</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Employee record saved successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2024-12-13 23:22:31</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20241213-009</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Added new employee record</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2024-12-13 23:24:07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>20241213-010</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Employee record saved successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2024-12-13 23:24:08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20241213-010</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Added new employee record</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2024-12-13 23:26:41</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>20241213-011</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Employee record saved successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2024-12-13 23:26:42</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20241213-011</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Added new employee record</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2024-12-13 23:30:35</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>20241213-001</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Employee record saved successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2024-12-13 23:30:36</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>20241213-001</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Added new employee record</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2024-12-13 23:32:35</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>20241213-002</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Employee record saved successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2024-12-13 23:32:36</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>20241213-002</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Added new employee record</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2024-12-13 23:34:44</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>20241213-003</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Employee record saved successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2024-12-13 23:34:45</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>20241213-003</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Added new employee record</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2024-12-13 23:35:31</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>20241213-004</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Employee record saved successfully</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2024-12-13 23:35:31</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>20241213-004</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Added new employee record</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
